--- a/out/Attention-Mamba1_repeat_2_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0002005738282697275</v>
+        <v>-0.0001636688423329033</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.2304208049272185</v>
+        <v>-0.1880240643416861</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.409276425334538</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.230783889720902</v>
+        <v>-0.1883260747498535</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5843524212818921</v>
+        <v>0.4974447647481483</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9390429308899962</v>
+        <v>0.807518566910563</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.04163495074181796</v>
+        <v>0.03544279846056585</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.437023119003372</v>
+        <v>0.3801615164153718</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.07301364601406558</v>
+        <v>0.06215472070976875</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5414014925428601</v>
+        <v>0.4690162580925238</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08870264527739027</v>
+        <v>0.07551033346157104</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6457868139451426</v>
+        <v>0.5578769143999671</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02347310741573422</v>
+        <v>0.01998209117329293</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6039165093381719</v>
+        <v>0.5222337322131374</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01304127828621855</v>
+        <v>0.01110133333463798</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.606503025443217</v>
+        <v>0.524435205552615</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02739887260565125</v>
+        <v>0.02332471371867403</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6482784225288964</v>
+        <v>0.5599976815272211</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.01076265559378019</v>
+        <v>0.009160405188812115</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6423778052419808</v>
+        <v>0.5549740140876814</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007662336675845507</v>
+        <v>0.006522154551495927</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6469370625198037</v>
+        <v>0.5588546135499594</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.003013592135033757</v>
+        <v>0.002564130148215865</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6452942165074579</v>
+        <v>0.5574552718611012</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00170751002854752</v>
+        <v>0.001453176855990958</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6456954278971746</v>
+        <v>0.5577961821150869</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0006479492922590374</v>
+        <v>0.0005504766461124544</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.645280904793848</v>
+        <v>0.5574424253714033</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0003010670032696959</v>
+        <v>0.0002559276250896328</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6452346250524069</v>
+        <v>0.5574022336493838</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0.0001072182159152025</v>
+        <v>9.026438473376897e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6451477377345134</v>
+        <v>0.5573274238088487</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.791201686447116e-05</v>
+        <v>2.314215934788113e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6450967139909421</v>
+        <v>0.557283022240226</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6450916879284708</v>
+        <v>0.557277999900965</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.732732469960194e-06</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6450879607171006</v>
+        <v>0.5572740905246162</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.274909021100856e-06</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6450862589982841</v>
+        <v>0.5572718395968845</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.645080593841292</v>
+        <v>0.5572662479368763</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6450739391108579</v>
+        <v>0.5572599239428684</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6450683875798203</v>
+        <v>0.55725455615429</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>-4.853353791035969e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6450634607290455</v>
+        <v>0.5572545929027817</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6450635709745212</v>
+        <v>0.5572547031482572</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6450636444715048</v>
+        <v>0.5572547766452408</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6450638282139639</v>
+        <v>0.5572549603876999</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6450653716506204</v>
+        <v>0.5572565038243564</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6450668415902935</v>
+        <v>0.5572579737640295</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6450680910390154</v>
+        <v>0.5572592232127516</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6450694507332128</v>
+        <v>0.5572605829069489</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6450672458237035</v>
+        <v>0.5572583779974396</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6450668415902935</v>
+        <v>0.5572579737640295</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.5572571285487176</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7769695850834732</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6450665476023587</v>
+        <v>0.5572576797760949</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6450662168659324</v>
+        <v>0.5572573490396685</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6450659228779979</v>
+        <v>0.557257055051734</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.5572571285487176</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6450655553930795</v>
+        <v>0.5572566875668157</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.645065445147604</v>
+        <v>0.5572565773213402</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6450654083991123</v>
+        <v>0.5572565405728485</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6450655553930795</v>
+        <v>0.5572566875668157</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6450650776626858</v>
+        <v>0.557256209836422</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6450660331234732</v>
+        <v>0.5572571652972093</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.5572571285487176</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6450656656385551</v>
+        <v>0.5572567978122912</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.645066106620457</v>
+        <v>0.5572572387941931</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6450654818960959</v>
+        <v>0.5572566140698321</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6450652981536368</v>
+        <v>0.5572564303273728</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6450648939202267</v>
+        <v>0.5572560260939629</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6450640487049147</v>
+        <v>0.5572551808786509</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.645064011956423</v>
+        <v>0.5572551441301592</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6450641589503903</v>
+        <v>0.5572552911241264</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6450640854534067</v>
+        <v>0.5572552176271428</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>4.409276425334538</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6450641589503903</v>
+        <v>0.5572552911241264</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6450641956988822</v>
+        <v>0.5572553278726183</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6450640854534067</v>
+        <v>0.5572552176271428</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6450645264353086</v>
+        <v>0.5572556586090447</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6450644161898331</v>
+        <v>0.5572555483635692</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6450643794413412</v>
+        <v>0.5572555116150772</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6450643059443575</v>
+        <v>0.5572554381180936</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6450642691958658</v>
+        <v>0.5572554013696019</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6450640487049147</v>
+        <v>0.5572551808786509</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6450639752079311</v>
+        <v>0.5572551073816673</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6450639017109475</v>
+        <v>0.5572550338846837</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6450639384594394</v>
+        <v>0.5572550706331756</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6450638282139639</v>
+        <v>0.5572549603876999</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6450639384594394</v>
+        <v>0.5572550706331756</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6450642324473739</v>
+        <v>0.55725536462111</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.6812199440383068</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383068</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383068</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0002005738282697275</v>
+        <v>-0.0001679221437554806</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.2304208049272185</v>
+        <v>-0.1929102907543774</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383072</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.2306213787554882</v>
+        <v>-0.1930782128981327</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.409276425334538</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.230783889720902</v>
+        <v>-0.1931768419218452</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5843524212818921</v>
+        <v>0.3546475074365772</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9390429308899962</v>
+        <v>0.5167991091523343</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.04163495074181796</v>
+        <v>0.0252685238582462</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.437023119003372</v>
+        <v>0.2121198292384415</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.07301364601406558</v>
+        <v>0.04431238132778189</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>4.409276425334538</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5414014925428601</v>
+        <v>0.2754678190850422</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08870264527739027</v>
+        <v>0.05383431006254988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6457868139451426</v>
+        <v>0.3388202090206903</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02347310741573422</v>
+        <v>0.01424590727181136</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6039165093381719</v>
+        <v>0.3134086873538175</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01304127828621855</v>
+        <v>0.007913210694727696</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.606503025443217</v>
+        <v>0.3149767932049171</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02739887260565125</v>
+        <v>0.01662947152354695</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6482784225288964</v>
+        <v>0.3403312386510391</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.01076265559378019</v>
+        <v>0.006529953276801027</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6423778052419808</v>
+        <v>0.3367481539721282</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007662336675845507</v>
+        <v>0.004648874994697677</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6469370625198037</v>
+        <v>0.3395132277789971</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.003013592135033757</v>
+        <v>0.001826795227242707</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6452942165074579</v>
+        <v>0.3385143212244967</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00170751002854752</v>
+        <v>0.001033912474564382</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6456954278971746</v>
+        <v>0.3387558259698828</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0006479492922590374</v>
+        <v>0.0003907624307397402</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.645280904793848</v>
+        <v>0.3385022403449987</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0003010670032696959</v>
+        <v>0.0001810623149373331</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6452346250524069</v>
+        <v>0.3384721458259213</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0.0001072182159152025</v>
+        <v>6.281532472573384e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6451477377345134</v>
+        <v>0.3384173659768135</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.791201686447116e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6450967139909421</v>
+        <v>0.3383842221056032</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6450916879284708</v>
+        <v>0.3383792064681205</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.732732469960194e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6450879607171006</v>
+        <v>0.3383750062587981</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.274909021100856e-06</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6450862589982841</v>
+        <v>0.3383720223796924</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.645080593841292</v>
+        <v>0.3383665786346861</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6450739391108579</v>
+        <v>0.3383605859012557</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6450683875798203</v>
+        <v>0.3383552181126773</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>-4.853353791035969e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6450634607290455</v>
+        <v>0.338355254861169</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6450635709745212</v>
+        <v>0.3383553651066446</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6450636444715048</v>
+        <v>0.3383554386036282</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6450638282139639</v>
+        <v>0.3383556223460873</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6450653716506204</v>
+        <v>0.3383571657827438</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6450668415902935</v>
+        <v>0.3383586357224169</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6450680910390154</v>
+        <v>0.3383598851711389</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6450694507332128</v>
+        <v>0.3383612448653362</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6450672458237035</v>
+        <v>0.3383590399558269</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6450668415902935</v>
+        <v>0.3383586357224169</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.338357790507105</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6450665476023587</v>
+        <v>0.3383583417344822</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6450662168659324</v>
+        <v>0.3383580109980558</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6450659228779979</v>
+        <v>0.3383577170101214</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.338357790507105</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6450655553930795</v>
+        <v>0.338357349525203</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.645065445147604</v>
+        <v>0.3383572392797274</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6450654083991123</v>
+        <v>0.3383572025312357</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383072</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6450655553930795</v>
+        <v>0.338357349525203</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>4.409276425334538</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6450650776626858</v>
+        <v>0.3383568717948093</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6450660331234732</v>
+        <v>0.3383578272555967</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6450659963749815</v>
+        <v>0.338357790507105</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6450656656385551</v>
+        <v>0.3383574597706785</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.645066106620457</v>
+        <v>0.3383579007525805</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6450654818960959</v>
+        <v>0.3383572760282194</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6450652981536368</v>
+        <v>0.3383570922857602</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6450648939202267</v>
+        <v>0.3383566880523502</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6450640487049147</v>
+        <v>0.3383558428370382</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.645064011956423</v>
+        <v>0.3383558060885465</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6450641589503903</v>
+        <v>0.3383559530825138</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383072</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6450640854534067</v>
+        <v>0.3383558795855302</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>4.409276425334538</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6450641589503903</v>
+        <v>0.3383559530825138</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383071</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6450641956988822</v>
+        <v>0.3383559898310057</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6450640854534067</v>
+        <v>0.3383558795855302</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.1670648583429531</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6450645264353086</v>
+        <v>0.3383563205674321</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6450644161898331</v>
+        <v>0.3383562103219566</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6450643794413412</v>
+        <v>0.3383561735734646</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6450643059443575</v>
+        <v>0.338356100076481</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6450642691958658</v>
+        <v>0.3383560633279893</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6450640487049147</v>
+        <v>0.3383558428370382</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6450639752079311</v>
+        <v>0.3383557693400546</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6450639017109475</v>
+        <v>0.338355695843071</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6450639384594394</v>
+        <v>0.3383557325915629</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6450638282139639</v>
+        <v>0.3383556223460873</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6450639384594394</v>
+        <v>0.3383557325915629</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6450642324473739</v>
+        <v>0.3383560265794974</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.003974702209234238</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.002415712922811508</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6812199440383068</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.002675216645002365</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.929504746419567</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.009039875119924545</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001643020659685135</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.929504746419567</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.003019735217094421</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.8812199440383068</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003971420228481293</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1670648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00531826913356781</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.005297273397445679</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.00617632269859314</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.006201963871717453</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.005928821861743927</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.006323512643575668</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.006019938737154007</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.003038093447685242</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.004721734672784805</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.006940886378288269</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.007188949733972549</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.00762505829334259</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.008204270154237747</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00826914981007576</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.008544169366359711</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008466314524412155</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.007702924311161041</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.007545284926891327</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.008384957909584045</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.008505057543516159</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.008550159633159637</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.008070949465036392</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.007098983973264694</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001766644418239594</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.004212502390146255</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005756165832281113</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.005544234067201614</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005875792354345322</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.00581500306725502</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.006228361278772354</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.006518755108118057</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.004688728600740433</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.00343632698059082</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.003526933491230011</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.001179862767457962</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8812199440383068</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002100192010402679</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.929504746419567</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.003280315548181534</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001679221437554806</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1929102907543774</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0001900158822536469</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.977789548800827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0003034882247447968</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.929504746419567</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001893244683742523</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8812199440383071</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001972280442714691</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002593416720628738</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003242790699005127</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003086403012275696</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00247684121131897</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002635877579450607</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002351302653551102</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002414952963590622</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002312265336513519</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001638863235712051</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8812199440383072</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1930782128981327</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0005395188927650452</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1931768419218452</v>
+        <v>-0.1413152098439792</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3546475074365772</v>
+        <v>0.3866971705496043</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0009392723441123962</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5167991091523343</v>
+        <v>0.6328216039830502</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0252685238582462</v>
+        <v>0.02755209221229843</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0008103400468826294</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2121198292384415</v>
+        <v>0.3006083131520255</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04431238132778189</v>
+        <v>0.04831698216083748</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>1.394748687744141e-05</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2754678190850422</v>
+        <v>0.3696809904884391</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05383431006254988</v>
+        <v>0.05869942713510714</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001301433891057968</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3388202090206903</v>
+        <v>0.4387582652113344</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01424590727181136</v>
+        <v>0.01553333914567821</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002600487321615219</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3134086873538175</v>
+        <v>0.4110505727412286</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007913210694727696</v>
+        <v>0.008628612207711016</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.001561813056468964</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.929504746419567</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3149767932049171</v>
+        <v>0.4127608036328733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01662947152354695</v>
+        <v>0.01813185613580216</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.000216066837310791</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.929504746419567</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3403312386510391</v>
+        <v>0.440405888840853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006529953276801027</v>
+        <v>0.007119746131842187</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0007225088775157928</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8812199440383071</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3367481539721282</v>
+        <v>0.4364995439891501</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004648874994697677</v>
+        <v>0.005069759167679973</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003321282565593719</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3395132277789971</v>
+        <v>0.43951513596091</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001826795227242707</v>
+        <v>0.00199245795350187</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003008376806974411</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3385143212244967</v>
+        <v>0.4384263431205321</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001033912474564382</v>
+        <v>0.00112793867775196</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.003585200756788254</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3387558259698828</v>
+        <v>0.4386901410130672</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003907624307397402</v>
+        <v>0.0004271678768908736</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003125648945569992</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3385022403449987</v>
+        <v>0.4384140897504338</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001810623149373331</v>
+        <v>0.0001975767215885757</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003192301839590073</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3384721458259213</v>
+        <v>0.438381767907178</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.281532472573384e-05</v>
+        <v>6.927392708056564e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002442702651023865</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3384173659768135</v>
+        <v>0.4383225691068454</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.503340156967809e-05</v>
+        <v>1.69413445763141e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002442847937345505</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3383842221056032</v>
+        <v>0.4382871071020824</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002636503428220749</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3383792064681205</v>
+        <v>0.4382820899753154</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.002287313342094421</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3383750062587981</v>
+        <v>0.4382779265144847</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003320474177598953</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3383720223796924</v>
+        <v>0.438275125368607</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002585187554359436</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3383665786346861</v>
+        <v>0.4382696816236006</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002788018435239792</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3383605859012557</v>
+        <v>0.4382636888901703</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002770006656646729</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3383552181126773</v>
+        <v>0.4382583211015919</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002590179443359375</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.338355254861169</v>
+        <v>0.4382583578500836</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002632714807987213</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3383553651066446</v>
+        <v>0.4382584680955592</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003061003983020782</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3383554386036282</v>
+        <v>0.4382585415925428</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002081185579299927</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3383556223460873</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-4.552677273750305e-05</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3383571657827438</v>
+        <v>0.4382602687716584</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.009465761482715607</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3383586357224169</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01558570563793182</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3383598851711389</v>
+        <v>0.4382629881600535</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01353847235441208</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3383612448653362</v>
+        <v>0.4382643478542508</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02793328836560249</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3383590399558269</v>
+        <v>0.4382621429447415</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0133945606648922</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3383586357224169</v>
+        <v>0.4382617387113315</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01817409321665764</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.338357790507105</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.009140625596046448</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3383583417344822</v>
+        <v>0.4382614447233968</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.007835026830434799</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3383580109980558</v>
+        <v>0.4382611139869704</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005880299955606461</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3383577170101214</v>
+        <v>0.4382608199990359</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.00509759783744812</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.338357790507105</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004949424415826797</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.338357349525203</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004193350672721863</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3383572392797274</v>
+        <v>0.438260342268642</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003814641386270523</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3383572025312357</v>
+        <v>0.4382603055201503</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003222301602363586</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8812199440383072</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.338357349525203</v>
+        <v>0.4382604525141176</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0006539672613143921</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3383568717948093</v>
+        <v>0.4382599747837239</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0009516812860965729</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3383578272555967</v>
+        <v>0.4382609302445112</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005444709211587906</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.338357790507105</v>
+        <v>0.4382608934960195</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004468269646167755</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3383574597706785</v>
+        <v>0.4382605627595931</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.005441665649414062</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3383579007525805</v>
+        <v>0.4382610037414951</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003757674247026443</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3383572760282194</v>
+        <v>0.4382603790171339</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002992011606693268</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3383570922857602</v>
+        <v>0.4382601952746748</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002117123454809189</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3383566880523502</v>
+        <v>0.4382597910412648</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002319216728210449</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3383558428370382</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002539791166782379</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3383558060885465</v>
+        <v>0.4382589090774611</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001919183880090714</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3383559530825138</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002525318413972855</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8812199440383072</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3383558795855302</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0005222968757152557</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3383559530825138</v>
+        <v>0.4382590560714283</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002582725137472153</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8812199440383071</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3383559898310057</v>
+        <v>0.4382590928199203</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.001199517399072647</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3383558795855302</v>
+        <v>0.4382589825744447</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003045022487640381</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3383563205674321</v>
+        <v>0.4382594235563467</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002746056765317917</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3383562103219566</v>
+        <v>0.4382593133108711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003595631569623947</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3383561735734646</v>
+        <v>0.4382592765623792</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003143589943647385</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.338356100076481</v>
+        <v>0.4382592030653956</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003360982984304428</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3383560633279893</v>
+        <v>0.4382591663169039</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003651615232229233</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3383558428370382</v>
+        <v>0.4382589458259528</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003057688474655151</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3383557693400546</v>
+        <v>0.4382588723289692</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003550726920366287</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.338355695843071</v>
+        <v>0.4382587988319855</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.00343216210603714</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3383557325915629</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00324142724275589</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3383556223460873</v>
+        <v>0.4382587253350019</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.001728653907775879</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7200000000000006</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3383557325915629</v>
+        <v>0.4382588355804775</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001946527510881424</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3670648583429531</v>
+        <v>1.140000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3383560265794974</v>
+        <v>0.438259129568412</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.003974702209234238</v>
+        <v>-0.003974713385105133</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.01999999999999985</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.002415712922811508</v>
+        <v>-0.002415694296360016</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1200000000000001</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.002675216645002365</v>
+        <v>0.00267520546913147</v>
       </c>
       <c r="JB4" t="n">
         <v>0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.009039875119924545</v>
+        <v>0.009039882570505142</v>
       </c>
       <c r="JB5" t="n">
         <v>0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.001643020659685135</v>
+        <v>0.001643050462007523</v>
       </c>
       <c r="JB6" t="n">
         <v>0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.003019735217094421</v>
+        <v>-0.003019742667675018</v>
       </c>
       <c r="JB7" t="n">
         <v>0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.003971420228481293</v>
+        <v>-0.003971409052610397</v>
       </c>
       <c r="JB8" t="n">
         <v>0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.00531826913356781</v>
+        <v>-0.005318257957696915</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.00617632269859314</v>
+        <v>-0.00617634505033493</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.006201963871717453</v>
+        <v>-0.006201945245265961</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.005928821861743927</v>
+        <v>-0.005928870290517807</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.006323512643575668</v>
+        <v>-0.006323534995317459</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.006019938737154007</v>
+        <v>-0.006019927561283112</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.003038093447685242</v>
+        <v>-0.003038115799427032</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.004721734672784805</v>
+        <v>-0.004721727222204208</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.006940886378288269</v>
+        <v>-0.006940867751836777</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.2599999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.00762505829334259</v>
+        <v>-0.007625062018632889</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.008204270154237747</v>
+        <v>-0.008204258978366852</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.00826914981007576</v>
+        <v>-0.008269175887107849</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.008544169366359711</v>
+        <v>-0.008544143289327621</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.008466314524412155</v>
+        <v>-0.008466329425573349</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.007702924311161041</v>
+        <v>-0.007702961564064026</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.007545284926891327</v>
+        <v>-0.007545262575149536</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.008384957909584045</v>
+        <v>-0.008384969085454941</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.008505057543516159</v>
+        <v>-0.008505061268806458</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.008550159633159637</v>
+        <v>-0.008550152182579041</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.008070949465036392</v>
+        <v>-0.008070934563875198</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.1199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.007098983973264694</v>
+        <v>-0.007098954170942307</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.001766644418239594</v>
+        <v>-0.00176665186882019</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.004212502390146255</v>
+        <v>-0.004212524741888046</v>
       </c>
       <c r="JB33" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.005544234067201614</v>
+        <v>-0.005544237792491913</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.005875792354345322</v>
+        <v>-0.005875799804925919</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.00581500306725502</v>
+        <v>-0.005814995616674423</v>
       </c>
       <c r="JB37" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.006228361278772354</v>
+        <v>-0.006228368729352951</v>
       </c>
       <c r="JB38" t="n">
         <v>0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.006518755108118057</v>
+        <v>-0.006518740206956863</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.004688728600740433</v>
+        <v>-0.004688713699579239</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.00343632698059082</v>
+        <v>-0.003436315804719925</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.003526933491230011</v>
+        <v>-0.003526955842971802</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.001179862767457962</v>
+        <v>-0.001179832965135574</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002100192010402679</v>
+        <v>0.002100210636854172</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.003280315548181534</v>
+        <v>0.003280322998762131</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0001900158822536469</v>
+        <v>0.0001900084316730499</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.0003034882247447968</v>
+        <v>0.0003035105764865875</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001893244683742523</v>
+        <v>-0.001893248409032822</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001972280442714691</v>
+        <v>-0.00197228416800499</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.002593416720628738</v>
+        <v>-0.00259341299533844</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.3</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.003242790699005127</v>
+        <v>-0.003242809325456619</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.003086403012275696</v>
+        <v>-0.00308641791343689</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.3</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.00247684121131897</v>
+        <v>-0.002476878464221954</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.16</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002635877579450607</v>
+        <v>-0.002635866403579712</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002351302653551102</v>
+        <v>-0.002351298928260803</v>
       </c>
       <c r="JB55" t="n">
         <v>0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002414952963590622</v>
+        <v>-0.002414926886558533</v>
       </c>
       <c r="JB56" t="n">
         <v>0.8599999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002312265336513519</v>
+        <v>-0.002312257885932922</v>
       </c>
       <c r="JB57" t="n">
         <v>0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.001638863235712051</v>
+        <v>-0.001638859510421753</v>
       </c>
       <c r="JB58" t="n">
         <v>0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0005395188927650452</v>
+        <v>0.0005395300686359406</v>
       </c>
       <c r="JB59" t="n">
         <v>0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0009392723441123962</v>
+        <v>-0.0009392611682415009</v>
       </c>
       <c r="JB60" t="n">
         <v>0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0008103400468826294</v>
+        <v>-0.0008103437721729279</v>
       </c>
       <c r="JB61" t="n">
         <v>0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1.394748687744141e-05</v>
+        <v>1.392513513565063e-05</v>
       </c>
       <c r="JB62" t="n">
         <v>0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001301433891057968</v>
+        <v>-0.00130143016576767</v>
       </c>
       <c r="JB63" t="n">
         <v>0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002600487321615219</v>
+        <v>-0.002600476145744324</v>
       </c>
       <c r="JB64" t="n">
         <v>0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.001561813056468964</v>
+        <v>0.001561786979436874</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.02000000000000007</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.000216066837310791</v>
+        <v>0.0002160370349884033</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.0007225088775157928</v>
+        <v>-0.0007225051522254944</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003321282565593719</v>
+        <v>-0.003321267664432526</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003008376806974411</v>
+        <v>-0.003008339554071426</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.003585200756788254</v>
+        <v>-0.003585193306207657</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003125648945569992</v>
+        <v>-0.003125634044408798</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003192301839590073</v>
+        <v>-0.003192294389009476</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002442702651023865</v>
+        <v>-0.002442732453346252</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002442847937345505</v>
+        <v>-0.002442825585603714</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002636503428220749</v>
+        <v>-0.002636518329381943</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.002287313342094421</v>
+        <v>-0.002287309616804123</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003320474177598953</v>
+        <v>-0.003320466727018356</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002585187554359436</v>
+        <v>-0.002585168927907944</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002788018435239792</v>
+        <v>-0.002788040786981583</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002770006656646729</v>
+        <v>-0.002769999206066132</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002590179443359375</v>
+        <v>-0.002590194344520569</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002632714807987213</v>
+        <v>-0.002632703632116318</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.2599999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003061003983020782</v>
+        <v>-0.003061000257730484</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002081185579299927</v>
+        <v>-0.002081193029880524</v>
       </c>
       <c r="JB84" t="n">
         <v>0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-4.552677273750305e-05</v>
+        <v>-4.554539918899536e-05</v>
       </c>
       <c r="JB85" t="n">
         <v>0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.009465761482715607</v>
+        <v>-0.009465765208005905</v>
       </c>
       <c r="JB86" t="n">
         <v>0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.01558570563793182</v>
+        <v>-0.01558571308851242</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.01353847235441208</v>
+        <v>-0.0135384239256382</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3999999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.02793328836560249</v>
+        <v>-0.0279332622885704</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0133945606648922</v>
+        <v>-0.0133945532143116</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.009140625596046448</v>
+        <v>-0.009140651673078537</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.007835026830434799</v>
+        <v>-0.007835004478693008</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.005880299955606461</v>
+        <v>-0.005880288779735565</v>
       </c>
       <c r="JB94" t="n">
         <v>0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.00509759783744812</v>
+        <v>-0.005097586661577225</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.004949424415826797</v>
+        <v>-0.004949405789375305</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.004193350672721863</v>
+        <v>-0.004193346947431564</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.003814641386270523</v>
+        <v>-0.003814674913883209</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.003222301602363586</v>
+        <v>-0.003222312778234482</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0006539672613143921</v>
+        <v>0.0006539560854434967</v>
       </c>
       <c r="JB100" t="n">
         <v>0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.0009516812860965729</v>
+        <v>-0.0009517073631286621</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005444709211587906</v>
+        <v>-0.005444739013910294</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.004468269646167755</v>
+        <v>-0.004468262195587158</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.16</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.005441665649414062</v>
+        <v>-0.005441684275865555</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003757674247026443</v>
+        <v>-0.003757677972316742</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.002992011606693268</v>
+        <v>-0.002991985529661179</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.02000000000000007</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.002117123454809189</v>
+        <v>-0.002117108553647995</v>
       </c>
       <c r="JB107" t="n">
         <v>0.1199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002539791166782379</v>
+        <v>-0.002539779990911484</v>
       </c>
       <c r="JB109" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0005222968757152557</v>
+        <v>0.0005223043262958527</v>
       </c>
       <c r="JB112" t="n">
         <v>0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002582725137472153</v>
+        <v>-0.002582710236310959</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.001199517399072647</v>
+        <v>-0.001199521124362946</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.02000000000000007</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003045022487640381</v>
+        <v>-0.003045029938220978</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002746056765317917</v>
+        <v>-0.002746060490608215</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003595631569623947</v>
+        <v>-0.003595635294914246</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003143589943647385</v>
+        <v>-0.003143571317195892</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003651615232229233</v>
+        <v>-0.00365162268280983</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003057688474655151</v>
+        <v>-0.003057718276977539</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003550726920366287</v>
+        <v>-0.003550756722688675</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.00343216210603714</v>
+        <v>-0.003432150930166245</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.00324142724275589</v>
+        <v>-0.003241445869207382</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.001728653907775879</v>
+        <v>-0.001728642731904984</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7200000000000006</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.001946527510881424</v>
+        <v>-0.001946572214365005</v>
       </c>
       <c r="JB126" t="n">
         <v>1.140000000000001</v>
